--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267072</v>
+        <v>130267076</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633202</v>
+        <v>633199</v>
       </c>
       <c r="R2" t="n">
-        <v>6659818</v>
+        <v>6659855</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,12 +752,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5  buketter</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,49 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267076</v>
+        <v>130267072</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>97794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633199</v>
+        <v>633202</v>
       </c>
       <c r="R3" t="n">
-        <v>6659855</v>
+        <v>6659818</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -849,18 +855,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5  buketter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,7 +882,7 @@
         <v>130267062</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130267064</v>
       </c>
       <c r="B6" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130267081</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130267083</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>130267063</v>
       </c>
       <c r="B9" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>130267075</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>130271351</v>
       </c>
       <c r="B12" t="n">
-        <v>91651</v>
+        <v>91654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267076</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130267072</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267062</v>
       </c>
       <c r="B4" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130267071</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130267064</v>
       </c>
       <c r="B6" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130267081</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130267083</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>130267063</v>
       </c>
       <c r="B9" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>130267075</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>130271351</v>
       </c>
       <c r="B12" t="n">
-        <v>91654</v>
+        <v>91680</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267076</v>
+        <v>130267072</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>97821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633199</v>
+        <v>633202</v>
       </c>
       <c r="R2" t="n">
-        <v>6659855</v>
+        <v>6659818</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -752,18 +748,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5  buketter</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267072</v>
+        <v>130267076</v>
       </c>
       <c r="B3" t="n">
-        <v>97820</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633202</v>
+        <v>633199</v>
       </c>
       <c r="R3" t="n">
-        <v>6659818</v>
+        <v>6659855</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,12 +849,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5  buketter</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,7 +882,7 @@
         <v>130267062</v>
       </c>
       <c r="B4" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130267064</v>
       </c>
       <c r="B6" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130267081</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130267083</v>
       </c>
       <c r="B8" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>130267063</v>
       </c>
       <c r="B9" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>130267075</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>130271351</v>
       </c>
       <c r="B12" t="n">
-        <v>91680</v>
+        <v>91681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267072</v>
+        <v>130267076</v>
       </c>
       <c r="B2" t="n">
-        <v>97821</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633202</v>
+        <v>633199</v>
       </c>
       <c r="R2" t="n">
-        <v>6659818</v>
+        <v>6659855</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,12 +752,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5  buketter</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,49 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267076</v>
+        <v>130267072</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>97822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633199</v>
+        <v>633202</v>
       </c>
       <c r="R3" t="n">
-        <v>6659855</v>
+        <v>6659818</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -849,18 +855,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5  buketter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,7 +882,7 @@
         <v>130267062</v>
       </c>
       <c r="B4" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130267064</v>
       </c>
       <c r="B6" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130267081</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130267083</v>
       </c>
       <c r="B8" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>130267063</v>
       </c>
       <c r="B9" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>130267075</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>130271351</v>
       </c>
       <c r="B12" t="n">
-        <v>91681</v>
+        <v>91682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267076</v>
+        <v>130267072</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>97824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633199</v>
+        <v>633202</v>
       </c>
       <c r="R2" t="n">
-        <v>6659855</v>
+        <v>6659818</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -752,18 +748,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5  buketter</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267072</v>
+        <v>130267076</v>
       </c>
       <c r="B3" t="n">
-        <v>97822</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633202</v>
+        <v>633199</v>
       </c>
       <c r="R3" t="n">
-        <v>6659818</v>
+        <v>6659855</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -855,12 +849,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5  buketter</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -882,7 +882,7 @@
         <v>130267062</v>
       </c>
       <c r="B4" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130267071</v>
       </c>
       <c r="B5" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130267064</v>
       </c>
       <c r="B6" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130267081</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130267083</v>
       </c>
       <c r="B8" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>130267063</v>
       </c>
       <c r="B9" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>130267075</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>130271351</v>
       </c>
       <c r="B12" t="n">
-        <v>91682</v>
+        <v>91684</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267072</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130267076</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267062</v>
       </c>
       <c r="B4" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130267064</v>
       </c>
       <c r="B6" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130267081</v>
       </c>
       <c r="B7" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130267083</v>
       </c>
       <c r="B8" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>130267063</v>
       </c>
       <c r="B9" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>130267075</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -675,45 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267072</v>
+        <v>130267076</v>
       </c>
       <c r="B2" t="n">
-        <v>97828</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633202</v>
+        <v>633199</v>
       </c>
       <c r="R2" t="n">
-        <v>6659818</v>
+        <v>6659855</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,12 +752,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>5  buketter</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,49 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267076</v>
+        <v>130267072</v>
       </c>
       <c r="B3" t="n">
-        <v>98957</v>
+        <v>97828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633199</v>
+        <v>633202</v>
       </c>
       <c r="R3" t="n">
-        <v>6659855</v>
+        <v>6659818</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -849,18 +855,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5  buketter</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130267076</v>
       </c>
       <c r="B2" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130267072</v>
       </c>
       <c r="B3" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>130267062</v>
       </c>
       <c r="B4" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>130267071</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130267064</v>
       </c>
       <c r="B6" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>130267081</v>
       </c>
       <c r="B7" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130267083</v>
       </c>
       <c r="B8" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>130267063</v>
       </c>
       <c r="B9" t="n">
-        <v>97203</v>
+        <v>97216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>130267075</v>
       </c>
       <c r="B10" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98957</v>
+        <v>98970</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>130271351</v>
       </c>
       <c r="B12" t="n">
-        <v>91684</v>
+        <v>91696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 53870-2025 artfynd.xlsx
+++ b/artfynd/A 53870-2025 artfynd.xlsx
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130267076</v>
+        <v>130267062</v>
       </c>
       <c r="B2" t="n">
-        <v>98970</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633199</v>
+        <v>633301</v>
       </c>
       <c r="R2" t="n">
-        <v>6659855</v>
+        <v>6659722</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -752,18 +748,12 @@
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>5  buketter</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130267072</v>
+        <v>130267063</v>
       </c>
       <c r="B3" t="n">
-        <v>97841</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633202</v>
+        <v>633228</v>
       </c>
       <c r="R3" t="n">
-        <v>6659818</v>
+        <v>6659787</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130267062</v>
+        <v>130267064</v>
       </c>
       <c r="B4" t="n">
-        <v>97216</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633301</v>
+        <v>633215</v>
       </c>
       <c r="R4" t="n">
-        <v>6659722</v>
+        <v>6659858</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130267071</v>
+        <v>130271351</v>
       </c>
       <c r="B5" t="n">
-        <v>57859</v>
+        <v>91831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Enbärsmossarna NV, Upl</t>
+          <t>Enbärsmossarna V, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633218</v>
+        <v>633311</v>
       </c>
       <c r="R5" t="n">
-        <v>6659848</v>
+        <v>6659707</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130267064</v>
+        <v>130267071</v>
       </c>
       <c r="B6" t="n">
-        <v>97216</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633215</v>
+        <v>633218</v>
       </c>
       <c r="R6" t="n">
-        <v>6659858</v>
+        <v>6659848</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1170,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130267081</v>
+        <v>130267075</v>
       </c>
       <c r="B7" t="n">
-        <v>98970</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633203</v>
+        <v>633224</v>
       </c>
       <c r="R7" t="n">
-        <v>6659847</v>
+        <v>6659841</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1249,7 +1239,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>17  buketter</t>
+          <t>6  buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130267083</v>
+        <v>130267076</v>
       </c>
       <c r="B8" t="n">
-        <v>98970</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633188</v>
+        <v>633199</v>
       </c>
       <c r="R8" t="n">
-        <v>6659843</v>
+        <v>6659855</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1356,7 +1346,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1  bukett</t>
+          <t>5  buketter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1384,45 +1374,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130267063</v>
+        <v>130267081</v>
       </c>
       <c r="B9" t="n">
-        <v>97216</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633228</v>
+        <v>633203</v>
       </c>
       <c r="R9" t="n">
-        <v>6659787</v>
+        <v>6659847</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1457,12 +1451,18 @@
           <t>2025-12-22</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>17  buketter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130267075</v>
+        <v>130267083</v>
       </c>
       <c r="B10" t="n">
-        <v>98970</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633224</v>
+        <v>633188</v>
       </c>
       <c r="R10" t="n">
-        <v>6659841</v>
+        <v>6659843</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>6  buketter</t>
+          <t>1  bukett</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,7 +1591,7 @@
         <v>130277260</v>
       </c>
       <c r="B11" t="n">
-        <v>98970</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,48 +1695,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130271351</v>
+        <v>130267072</v>
       </c>
       <c r="B12" t="n">
-        <v>91696</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3242</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Enbärsmossarna V, Upl</t>
+          <t>Enbärsmossarna NV, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633311</v>
+        <v>633202</v>
       </c>
       <c r="R12" t="n">
-        <v>6659707</v>
+        <v>6659818</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
